--- a/data/raw/individual/ID 008/continuous/mHLEA_excel/TUM_S008_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 008/continuous/mHLEA_excel/TUM_S008_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 008/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 008/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D250D24-2BEE-9846-83E9-6DAF20ABE4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A7B3C9-264D-0A46-8DBC-EB6308D76CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,13 +80,13 @@
     <t>L+I+E</t>
   </si>
   <si>
-    <t>8: sports</t>
+    <t>shfting</t>
   </si>
   <si>
-    <t>8: pray</t>
+    <t>pray</t>
   </si>
   <si>
-    <t>8: shfting</t>
+    <t>sports</t>
   </si>
 </sst>
 </file>
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>45482.291666666591</v>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>45482.333333333256</v>
@@ -854,7 +854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>45482.37499999992</v>
@@ -866,7 +866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>45482.416666666584</v>
@@ -878,7 +878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>45482.458333333248</v>
@@ -890,7 +890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>45482.499999999913</v>
@@ -902,7 +902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>45482.541666666577</v>
@@ -914,7 +914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>45482.583333333241</v>
@@ -926,7 +926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>45482.624999999905</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>45482.66666666657</v>
@@ -950,7 +950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>45482.708333333234</v>
@@ -962,7 +962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>45482.749999999898</v>
@@ -970,11 +970,14 @@
       <c r="B44" t="s">
         <v>6</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>45482.791666666562</v>
@@ -982,11 +985,14 @@
       <c r="B45" t="s">
         <v>6</v>
       </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C45">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45482.833333333227</v>
@@ -998,7 +1004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>45482.874999999891</v>
@@ -1010,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>45482.916666666555</v>
@@ -1406,7 +1412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>45484.291666666475</v>
@@ -1418,7 +1424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>45484.333333333139</v>
@@ -1430,7 +1436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>45484.374999999804</v>
@@ -1442,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>45484.416666666468</v>
@@ -1454,7 +1460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>45484.458333333132</v>
@@ -1466,7 +1472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>45484.499999999796</v>
@@ -1478,7 +1484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>45484.541666666461</v>
@@ -1490,7 +1496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>45484.583333333125</v>
@@ -1502,7 +1508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>45484.624999999789</v>
@@ -1514,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>45484.666666666453</v>
@@ -1526,7 +1532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>45484.708333333117</v>
@@ -1534,11 +1540,14 @@
       <c r="B91" t="s">
         <v>6</v>
       </c>
-      <c r="C91" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C91">
+        <v>8</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>45484.749999999782</v>
@@ -1546,11 +1555,14 @@
       <c r="B92" t="s">
         <v>6</v>
       </c>
-      <c r="C92" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>45484.791666666446</v>
@@ -1558,11 +1570,14 @@
       <c r="B93" t="s">
         <v>6</v>
       </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C93">
+        <v>8</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>45484.83333333311</v>
@@ -1574,7 +1589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>45484.874999999774</v>
@@ -1586,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>45484.916666666439</v>
@@ -1598,7 +1613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>45484.958333333103</v>
@@ -1610,7 +1625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>45484.999999999767</v>
@@ -1622,7 +1637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>45485.041666666431</v>
@@ -1634,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>45485.083333333096</v>
@@ -1646,7 +1661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>45485.12499999976</v>
@@ -1658,7 +1673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>45485.166666666424</v>
@@ -1670,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>45485.208333333088</v>
@@ -1682,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>45485.249999999753</v>
@@ -1694,7 +1709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>45485.291666666417</v>
@@ -1706,7 +1721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>45485.333333333081</v>
@@ -1718,7 +1733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>45485.374999999745</v>
@@ -1730,7 +1745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>45485.41666666641</v>
@@ -1742,7 +1757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <f t="shared" si="1"/>
         <v>45485.458333333074</v>
@@ -1754,7 +1769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>45485.499999999738</v>
@@ -1766,7 +1781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>45485.541666666402</v>
@@ -1774,11 +1789,14 @@
       <c r="B111" t="s">
         <v>6</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111">
+        <v>8</v>
+      </c>
+      <c r="D111" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>45485.583333333067</v>
@@ -1786,7 +1804,10 @@
       <c r="B112" t="s">
         <v>6</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112">
+        <v>8</v>
+      </c>
+      <c r="D112" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1982,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>45486.291666666359</v>
@@ -1994,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>45486.333333333023</v>
@@ -2006,7 +2027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>45486.374999999687</v>
@@ -2018,7 +2039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" ref="A132:A169" si="2">A131 + TIME(1, 0, 0)</f>
         <v>45486.416666666351</v>
@@ -2026,11 +2047,14 @@
       <c r="B132" t="s">
         <v>5</v>
       </c>
-      <c r="C132" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C132">
+        <v>8</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" si="2"/>
         <v>45486.458333333016</v>
@@ -2038,11 +2062,14 @@
       <c r="B133" t="s">
         <v>5</v>
       </c>
-      <c r="C133" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C133">
+        <v>8</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>45486.49999999968</v>
@@ -2054,7 +2081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>45486.541666666344</v>
@@ -2066,7 +2093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>45486.583333333008</v>
@@ -2078,7 +2105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>45486.624999999673</v>
@@ -2090,7 +2117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>45486.666666666337</v>
@@ -2102,7 +2129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>45486.708333333001</v>
@@ -2114,7 +2141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>45486.749999999665</v>
@@ -2126,7 +2153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>45486.79166666633</v>
@@ -2138,7 +2165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>45486.833333332994</v>
@@ -2150,7 +2177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>45486.874999999658</v>
@@ -2162,7 +2189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>45486.916666666322</v>
